--- a/output/北塩原村_福島県計画との整合.xlsx
+++ b/output/北塩原村_福島県計画との整合.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_このブックについて" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_県の計画" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01b_県の成果目標" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_指針が求める県との関係" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_県への確認事項" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_素案への反映" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01c_会津圏域計画" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_指針が求める県との関係" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_県への確認事項" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_素案への反映" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1163,6 +1164,213 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>県計画 第9「圏域計画」の会津障がい保健福祉圏域計画と本村への意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本村は会津障がい保健福祉圏域（2市8町3村）に属する。県計画は圏域ごとに現状と課題・方策・令和8年度の数値目標・見込量・新たに必要となる事業所数を定めており、本村に直接かかわる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>県計画の記載（原典）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>本村への意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>圏域の構成</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>会津若松市、喜多方市、北塩原村、西会津町、磐梯町、猪苗代町、会津坂下町、湯川村、柳津町、三島町、金山町、昭和村、会津美里町（2市8町3村）。圏域人口222,124人（0〜17歳29,624人・18〜64歳109,379人・65歳以上80,650人。令和5年4月1日）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>見込量の進行管理と県との計画協議はこの区域を単位として行われる。本計画がいう「会津北部圏域」（4町村）とは範囲が異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>「会津圏域では、会津若松市、喜多方市、会津北部、会津西部の4つの拠点が整備されています」。未整備地域の解消と拠点の機能の充実が課題。令和8年度の数値目標は13市町村・5か所、コーディネーター7人、検証及び検討の実施18回</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>県計画が「会津北部」を拠点の単位として挙げている。本計画が会津北部圏域での共同整備を前提とすることは県計画と整合する。計画素案 第1章2に根拠として明記した</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>基幹相談支援センター</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の数値目標は13市町村（圏域の全市町村）。令和5年4月1日現在の設置は2か所（会津若松市1・喜多方市1）。「基幹相談支援センターが設置されていない市町村に対して設置促進を図り、基幹相談支援センターの機能を活かすことにより、地域全体の相談支援体制の充実・強化に取り組むことが求められています」</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>県全体では令和4年度実績44市町村が設置済みであり、会津圏域の2か所は大きく遅れている。本村の未設置は圏域全体の課題。県は相談支援アドバイザーを活用した設置支援を方策に掲げており、4町村での広域設置の検討にこれを求める。計画素案 第4章（6）に反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>施設入所者の地域生活移行</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>令和4年度末の施設入所者278人、令和8年度末の地域生活移行者9人（3％以上）、削減見込12人（4％以上）、令和8年度末266人。課題は障がいの重度化・高齢化と重度障がい者・高齢障がい者の受け皿</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>本村の施設入所者は4人。圏域目標と同じ3％・4％を当てるといずれも1人未満になる。村の移行0人・削減0人は圏域目標と矛盾しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>一般就労への移行</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>令和3年度16人→令和8年度32人（2.0倍）。うち就労移行支援6→11人、A型3→7人、B型7→14人。就労定着支援の利用者数10→24人（2.4倍）。令和8年度の就労移行支援事業所2か所・就労定着支援事業所2か所はいずれも一般就労移行5割以上・定着率7割以上が100％</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>本村の一般就労移行者数は少数。圏域の目標倍率（2.0倍）は国の基本指針（1.28倍以上）を大きく上回る。第4章（3）の目標設定で圏域の水準に触れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>新たに必要となる事業所数</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>令和5年4月1日→令和8年度：就労選択支援0→2か所（新設）、就労継続支援A型6→8か所、同B型30→32か所、共同生活援助34→36か所、自立生活援助0→1か所（新設）、自立訓練（機能訓練）0→1か所（新設）、就労移行支援2→3か所、就労定着支援2→3か所、生活介護22→23か所。施設入所支援4か所・療養介護0か所・短期入所（福祉系11・医療系1）は据え置き</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>本村が圏域の事業所を利用して確保する前提は、この整備計画に沿う。計画素案 第5章8に反映。第8期県計画の公表後に同じ箇所を見直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>障がい児支援の整備状況</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>令和5年4月1日現在。児童発達支援センター1か所（会津若松市）、児童発達支援事業所20か所（会津若松市13・喜多方市3・猪苗代町1・会津坂下町2・湯川村1）、放課後等デイサービス23か所（会津若松市14・喜多方市3・磐梯町1・猪苗代町1・会津坂下町2・湯川村1・会津美里町1）、保育所等訪問支援6か所（会津若松市）、障害児相談支援18か所、短期入所（福祉型・児童利用可）1か所（猪苗代町）、福祉型障害児入所施設1か所（猪苗代町）。医療型の児童発達支援センター・事業所・入所施設はいずれも0か所</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>児童発達支援センターと保育所等訪問支援は会津若松市のみで本村から遠い。短期入所（児童）と福祉型障害児入所施設は猪苗代町＝会津北部圏域の内。第4章（4）の4つの中核機能へのアクセス確保の具体に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>障がい児支援の見込量</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>令和8年度（圏域）：障害児相談支援653人、児童発達支援257人（1,320人日／月）、放課後等デイサービス458人（4,424人日／月）、保育所等訪問支援120人（108人日／月）、居宅訪問型児童発達支援2人。必要な事業所数は児童発達支援24か所・放課後等デイサービス27か所・保育所等訪問支援6か所</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>本村の障がい児の見込量（児童発達支援1人・放課後等デイサービス2人等）は圏域の規模に対してごく小さい。確保は圏域の事業所に依存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>圏域の推進体制</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>会津障がい保健福祉圏域連絡会の下部組織に8つのワーキンググループ（精神保健福祉、就労、事業所、重点検討事項ほか）を置き、ワーキンググループ長会議とサービス調整会議で横の連携を図る。相談支援事業所は圏域に22か所</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>本村が圏域で課題を持ち込む先が具体的に分かる。強度行動障害の支援、権利擁護、BCP・個別避難計画もワーキンググループでの検討事項とされている</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1279,7 +1487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1480,13 +1688,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1600,86 +1808,152 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>第5章1</t>
+          <t>第4章（6）</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>告示 第三の二の2㈠が「設定するものとする」とした2要件（継続入所者の控除・保育所等における障害児の受入れ体制）を算定方法の根拠の表に追加し、村への照会を最優先として明記</t>
+          <t>基幹相談支援センターについて、県全体59市町村（令和4年度実績44市町村）・会津圏域13市町村の目標と、圏域の設置が2か所（会津若松市・喜多方市）にとどまる事実、県の相談支援アドバイザーによる設置支援を追記</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>告示 第三の二の2㈠。見込量算定MECEチェックの指摘E-1・E-2</t>
+          <t>第7期県計画 第3の5（p.34）・会津圏域計画6(4)・第3期県計画の会津圏域計画（障がい児支援）3</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>素案の本文に2要件が現れることを確認（告示本文のPDFと照合）</t>
+          <t>設置市町村数と圏域の設置実績を原典と機械で照合</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>第5章7・第5章冒頭</t>
+          <t>第4章（4）</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>廃止区分「医療型児童発達支援」を≪サービスの内容≫とサービス区分表から削除し、②〜⑦の番号を繰り上げ</t>
+          <t>会津圏域の障がい児支援事業所の所在を表で追記。児童発達支援センターと保育所等訪問支援は会津若松市のみ、短期入所（児童）と福祉型障害児入所施設は猪苗代町</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>令和4年法律第66号による児童福祉法の改正（令和6年4月1日施行）。見込量MECEチェックの指摘X-1</t>
+          <t>第3期福島県障がい児福祉計画 会津圏域計画（障がい児支援）3</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>生成器の自己点検で、表の行名に廃止区分がないこと及びサービスの内容が①〜⑥の連番であることを確認</t>
+          <t>事業所数と市町村ごとの内訳を原典と機械で照合</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>第5章冒頭・第5章7・第5章9</t>
+          <t>第5章8</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>「R6～R8実績」「R9～R11見込量」等の略記の年度表記を令和表記に統一</t>
+          <t>会津圏域が令和8年度までに新たに必要とする事業所数を追記（就労選択支援2か所の新設、就労継続支援A型6→8・B型30→32、共同生活援助34→36ほか）</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>注記が差し替え前の列名を指したままになっていた</t>
+          <t>第7期県計画 会津圏域計画8</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>生成器の自己点検で、表頭と注記に略記の年度表記がないことを確認</t>
+          <t>事業所数の推移を原典と機械で照合</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
+          <t>第5章1</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>告示 第三の二の2㈠が「設定するものとする」とした2要件（継続入所者の控除・保育所等における障害児の受入れ体制）を算定方法の根拠の表に追加し、村への照会を最優先として明記</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>告示 第三の二の2㈠。見込量算定MECEチェックの指摘E-1・E-2</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>素案の本文に2要件が現れることを確認（告示本文のPDFと照合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>第5章7・第5章冒頭</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>廃止区分「医療型児童発達支援」を≪サービスの内容≫とサービス区分表から削除し、②〜⑦の番号を繰り上げ</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>令和4年法律第66号による児童福祉法の改正（令和6年4月1日施行）。見込量MECEチェックの指摘X-1</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>生成器の自己点検で、表の行名に廃止区分がないこと及びサービスの内容が①〜⑥の連番であることを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>第5章冒頭・第5章7・第5章9</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>「R6～R8実績」「R9～R11見込量」等の略記の年度表記を令和表記に統一</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>注記が差し替え前の列名を指したままになっていた</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>生成器の自己点検で、表頭と注記に略記の年度表記がないことを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
           <t>生成器</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>計画素案の生成器に保存前の自己点検（verify_output）を追加。見込量表5件がデータ行を持つこと、廃止区分が行名に残らないこと、番号が連番であることを保存前に確かめる</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>注記ボックスは1x1の表であるため、見込量表の直前に差し込むと見込量表と取り違えられ、見込量が消えたまま警告なく保存される。本日の作業で実際に起こした</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>点検に落ちることを確認した上で原因を直した</t>
         </is>

--- a/output/北塩原村_福島県計画との整合.xlsx
+++ b/output/北塩原村_福島県計画との整合.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_このブックについて" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_県の計画" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01b_県の成果目標" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01c_会津圏域計画" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_指針が求める県との関係" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_県への確認事項" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_素案への反映" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01d_県障がい者計画" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01c_会津圏域計画" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_指針が求める県との関係" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_県への確認事項" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_素案への反映" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,12 +919,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>福島県障がい者計画（第5次）</t>
+          <t>第5次福島県障がい者計画</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>障害者基本法第11条第2項（都道府県障害者計画）</t>
+          <t>障害者基本法第11条第2項（都道府県障害者計画）。障害者文化芸術活動推進法第8条及び読書バリアフリー法第8条に基づく計画としての性格も併せ持つ</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -931,19 +932,19 @@
           <t>令和4年度〜令和12年度（9年間）</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>二次</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>原典</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>手元にない。令和4年3月策定で、計画期間を9年とし終期を福島県総合計画及び福島県保健医療福祉復興ビジョンの目標年次に合わせている。素案に対する県民意見公募が令和4年2月4日から24日まで行われ、結果が同年4月8日に公表されている。計画期間は県ホームページ掲載の計画本文 第3「計画の期間」に記載があるが原典を取得できていない。なお第7期県計画がその実施計画であることは原典で確認済み</t>
+          <t>令和8年10月8日に本文テキストを受領し原典で確認（令和4年3月策定）。計画期間は「福島県総合計画」及び「福島県保健医療福祉復興ビジョン」との整合を図るため目標年度を合わせたもの（第1章第3）。福島県保健医療福祉復興ビジョンに連なる個別計画（第1章第2）。基本理念は「障がいのある方の人権、人格が尊重され、等しく社会の一員として生活できる社会の実現」で、4つの基本目標の下に9つの重点施策を置く</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>第1章2「■　福島県の計画との整合」の表。本計画期間（令和9〜11年度）は県障がい者計画の期間内に収まるため、本計画の障がい者計画部分は同計画の施策体系に即して組む</t>
+          <t>第1章2「■　福島県の計画との整合」及び「■　県障がい者計画の基本目標と本計画の施策体系」。本計画期間（令和9〜11年度）は同計画の期間内に完全に収まるため、本計画の障がい者計画部分は同計画の基本目標・重点施策と対応させる</t>
         </is>
       </c>
     </row>
@@ -1164,10 +1165,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="78" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1175,14 +1176,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>県計画 第9「圏域計画」の会津障がい保健福祉圏域計画と本村への意味</t>
+          <t>第5次福島県障がい者計画（令和4年3月）と本計画の対応</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本村は会津障がい保健福祉圏域（2市8町3村）に属する。県計画は圏域ごとに現状と課題・方策・令和8年度の数値目標・見込量・新たに必要となる事業所数を定めており、本村に直接かかわる。</t>
+          <t>令和8年10月8日に本文テキストを受領し、原典で確認した。引用は本ブックの自己点検で原典と照合している。</t>
         </is>
       </c>
     </row>
@@ -1199,160 +1200,194 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>本村への意味</t>
+          <t>本計画への反映</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>圏域の構成</t>
+          <t>計画期間（第1章第3）</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>会津若松市、喜多方市、北塩原村、西会津町、磐梯町、猪苗代町、会津坂下町、湯川村、柳津町、三島町、金山町、昭和村、会津美里町（2市8町3村）。圏域人口222,124人（0〜17歳29,624人・18〜64歳109,379人・65歳以上80,650人。令和5年4月1日）</t>
+          <t>「本計画の期間は、『福島県総合計画』及び『福島県保健医療福祉復興ビジョン』との整合を図るため、目標年度を合わせ、令和4年度から令和12年度までの9年間とします」</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>見込量の進行管理と県との計画協議はこの区域を単位として行われる。本計画がいう「会津北部圏域」（4町村）とは範囲が異なる</t>
+          <t>本計画期間（令和9〜11年度）は県障がい者計画の期間内に完全に収まる。当初の照会事項（Q-7）は解決。第1章2の表に原典で記載</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>地域生活支援拠点</t>
+          <t>位置付け（第1章第2）</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>「会津圏域では、会津若松市、喜多方市、会津北部、会津西部の4つの拠点が整備されています」。未整備地域の解消と拠点の機能の充実が課題。令和8年度の数値目標は13市町村・5か所、コーディネーター7人、検証及び検討の実施18回</t>
+          <t>福島県総合計画の部門別計画である福島県保健医療福祉復興ビジョンに連なる個別計画。障害者基本法第11条第2項の都道府県障害者計画。あわせて障害者文化芸術活動推進法第8条に基づく計画及び読書バリアフリー法第8条に基づく計画としての性格も併せ持つ</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>県計画が「会津北部」を拠点の単位として挙げている。本計画が会津北部圏域での共同整備を前提とすることは県計画と整合する。計画素案 第1章2に根拠として明記した</t>
+          <t>第1章2の表に記載。読書バリアフリー法に基づく読書環境の整備は本計画に記述がなく、情報アクセシビリティの検討事項に含める</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>基幹相談支援センター</t>
+          <t>基本理念（第1章第4）</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の数値目標は13市町村（圏域の全市町村）。令和5年4月1日現在の設置は2か所（会津若松市1・喜多方市1）。「基幹相談支援センターが設置されていない市町村に対して設置促進を図り、基幹相談支援センターの機能を活かすことにより、地域全体の相談支援体制の充実・強化に取り組むことが求められています」</t>
+          <t>「障がいのある方の人権、人格が尊重され、等しく社会の一員として生活できる社会の実現」〜障がいのある方もない方も、ともに生きる社会を目指して〜</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>県全体では令和4年度実績44市町村が設置済みであり、会津圏域の2か所は大きく遅れている。本村の未設置は圏域全体の課題。県は相談支援アドバイザーを活用した設置支援を方策に掲げており、4町村での広域設置の検討にこれを求める。計画素案 第4章（6）に反映</t>
+          <t>本村の基本理念「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」と趣旨が一致する。第3章1の基本理念は現行のまま据え置いて差し支えない</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>施設入所者の地域生活移行</t>
+          <t>基本目標（第1章第5）</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>令和4年度末の施設入所者278人、令和8年度末の地域生活移行者9人（3％以上）、削減見込12人（4％以上）、令和8年度末266人。課題は障がいの重度化・高齢化と重度障がい者・高齢障がい者の受け皿</t>
+          <t>4つ。1 地域生活への移行支援／2 自立した生活を送るための支援／3 活躍できる社会づくり／4 安全・安心で差別のない社会づくり</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>本村の施設入所者は4人。圏域目標と同じ3％・4％を当てるといずれも1人未満になる。村の移行0人・削減0人は圏域目標と矛盾しない</t>
+          <t>本村は3つの基本目標（①理解と交流／②支え合いと安心／③自立）。数は異なるが趣旨は包含関係にある。第1章2に対応表を置いた</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>一般就労への移行</t>
+          <t>計画の体系（第3章第1）</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>令和3年度16人→令和8年度32人（2.0倍）。うち就労移行支援6→11人、A型3→7人、B型7→14人。就労定着支援の利用者数10→24人（2.4倍）。令和8年度の就労移行支援事業所2か所・就労定着支援事業所2か所はいずれも一般就労移行5割以上・定着率7割以上が100％</t>
+          <t>4つの基本目標の下に9つの重点施策。①生活支援②保健・医療・福祉③ライフステージに応じた障がいのある子どもへの支援④文化芸術・スポーツ活動の振興、社会参加の促進⑤雇用・就業、経済的自立の支援⑥生活環境⑦障がいのある方のアクセシビリティの向上⑧安全・安心⑨差別の解消及び権利擁護の推進</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>本村の一般就労移行者数は少数。圏域の目標倍率（2.0倍）は国の基本指針（1.28倍以上）を大きく上回る。第4章（3）の目標設定で圏域の水準に触れる</t>
+          <t>本村の7つの基本施策との対応表を第1章2に新設。重点施策⑦（アクセシビリティの向上）に正面から対応する基本施策がなく、特に⑶行政等における配慮の定着は本計画に記述がない</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>新たに必要となる事業所数</t>
+          <t>県の条例（第1章第1）</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>令和5年4月1日→令和8年度：就労選択支援0→2か所（新設）、就労継続支援A型6→8か所、同B型30→32か所、共同生活援助34→36か所、自立生活援助0→1か所（新設）、自立訓練（機能訓練）0→1か所（新設）、就労移行支援2→3か所、就労定着支援2→3か所、生活介護22→23か所。施設入所支援4か所・療養介護0か所・短期入所（福祉系11・医療系1）は据え置き</t>
+          <t>平成31年4月に「障がいのある人もない人も共に暮らしやすい福島県づくり条例」及び「福島県手話言語条例」を施行</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>本村が圏域の事業所を利用して確保する前提は、この整備計画に沿う。計画素案 第5章8に反映。第8期県計画の公表後に同じ箇所を見直す</t>
+          <t>本村に独自の条例がないため、差別の解消（基本施策①）と意思疎通支援はこれらの県条例を根拠として記述できる。第1章2の注記に明記</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>障がい児支援の整備状況</t>
+          <t>主な課題等（第2章第3）</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>令和5年4月1日現在。児童発達支援センター1か所（会津若松市）、児童発達支援事業所20か所（会津若松市13・喜多方市3・猪苗代町1・会津坂下町2・湯川村1）、放課後等デイサービス23か所（会津若松市14・喜多方市3・磐梯町1・猪苗代町1・会津坂下町2・湯川村1・会津美里町1）、保育所等訪問支援6か所（会津若松市）、障害児相談支援18か所、短期入所（福祉型・児童利用可）1か所（猪苗代町）、福祉型障害児入所施設1か所（猪苗代町）。医療型の児童発達支援センター・事業所・入所施設はいずれも0か所</t>
+          <t>8項目。1 理解促進と差別解消／2 相談支援体制の充実（基幹相談支援センターの機能の充実など相談支援機能の強化）／3 地域生活への移行／4 就労支援の一層の充実／5 自殺対策／6 社会参加の促進／7 防災対策の充実（避難行動要支援者の把握、個別避難計画の作成及び関係機関での情報の共有）／8 東日本大震災及び原子力災害からの復興・創生</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>児童発達支援センターと保育所等訪問支援は会津若松市のみで本村から遠い。短期入所（児童）と福祉型障害児入所施設は猪苗代町＝会津北部圏域の内。第4章（4）の4つの中核機能へのアクセス確保の具体に用いる</t>
+          <t>本村の課題（第3章5・第4章）と重なる。特に2は本村の基幹相談支援センター未設置、7は個別避難計画の作成（第3章4の⑥生活環境）に直結する</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>障がい児支援の見込量</t>
+          <t>障がい保健福祉圏域（第3章第2）</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>令和8年度（圏域）：障害児相談支援653人、児童発達支援257人（1,320人日／月）、放課後等デイサービス458人（4,424人日／月）、保育所等訪問支援120人（108人日／月）、居宅訪問型児童発達支援2人。必要な事業所数は児童発達支援24か所・放課後等デイサービス27か所・保育所等訪問支援6か所</t>
+          <t>「7つの障がい保健福祉圏域を設定し、圏域ごとに、きめ細かなサービスの提供体制の確保・充実を進めていきます」</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>本村の障がい児の見込量（児童発達支援1人・放課後等デイサービス2人等）は圏域の規模に対してごく小さい。確保は圏域の事業所に依存する</t>
+          <t>県障がい福祉計画の区域の設定と同じ。本村は会津圏域。第1章2の区域の節と整合する</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>圏域の推進体制</t>
+          <t>進行管理（第1章第7）</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>会津障がい保健福祉圏域連絡会の下部組織に8つのワーキンググループ（精神保健福祉、就労、事業所、重点検討事項ほか）を置き、ワーキンググループ長会議とサービス調整会議で横の連携を図る。相談支援事業所は圏域に22か所</t>
+          <t>毎年度、実施状況を取りまとめ進捗状況を点検し、福島県障がい者施策推進協議会及び福島県自立支援協議会において評価</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>本村が圏域で課題を持ち込む先が具体的に分かる。強度行動障害の支援、権利擁護、BCP・個別避難計画もワーキンググループでの検討事項とされている</t>
+          <t>本村の点検評価（第1章6）と同じ年次。村の評価結果は県の点検に用いられるため、様式と時期を県に合わせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>入所支援施設の方針（第4章 基本目標1）</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>「入所支援施設については、これまでと同様に新たな施設の設置や定員の増加は原則として行わないこととし、既存施設の利用環境の改善や老朽施設の計画的な改修等により、安全で快適な利用環境の確保に努めます」</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>本村の施設入所支援の見込量（4人で据え置き）は、県の方針と整合する。第4章（1）の説明に引ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>65歳到達時の取扱い（第4章 基本目標1）</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>「65歳以上（40歳以上65歳未満の医療保険加入者を含む）の障がいのある方については、制度上、介護保険法の規定による保険給付が優先適用されますが、支給量が不足したり、介護保険に相当するサービスがない場合は、障害福祉サービスも併せて利用したり、利用者の状況に応じた適切な支給決定がなされるよう…努めます」</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>本計画 第5章2（年齢到達に伴うサービスの移行）の65歳到達時の記述と一致する。県計画を根拠として引ける</t>
         </is>
       </c>
     </row>
@@ -1371,6 +1406,213 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>県計画 第9「圏域計画」の会津障がい保健福祉圏域計画と本村への意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本村は会津障がい保健福祉圏域（2市8町3村）に属する。県計画は圏域ごとに現状と課題・方策・令和8年度の数値目標・見込量・新たに必要となる事業所数を定めており、本村に直接かかわる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>県計画の記載（原典）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>本村への意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>圏域の構成</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>会津若松市、喜多方市、北塩原村、西会津町、磐梯町、猪苗代町、会津坂下町、湯川村、柳津町、三島町、金山町、昭和村、会津美里町（2市8町3村）。圏域人口222,124人（0〜17歳29,624人・18〜64歳109,379人・65歳以上80,650人。令和5年4月1日）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>見込量の進行管理と県との計画協議はこの区域を単位として行われる。本計画がいう「会津北部圏域」（4町村）とは範囲が異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>「会津圏域では、会津若松市、喜多方市、会津北部、会津西部の4つの拠点が整備されています」。未整備地域の解消と拠点の機能の充実が課題。令和8年度の数値目標は13市町村・5か所、コーディネーター7人、検証及び検討の実施18回</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>県計画が「会津北部」を拠点の単位として挙げている。本計画が会津北部圏域での共同整備を前提とすることは県計画と整合する。計画素案 第1章2に根拠として明記した</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>基幹相談支援センター</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の数値目標は13市町村（圏域の全市町村）。令和5年4月1日現在の設置は2か所（会津若松市1・喜多方市1）。「基幹相談支援センターが設置されていない市町村に対して設置促進を図り、基幹相談支援センターの機能を活かすことにより、地域全体の相談支援体制の充実・強化に取り組むことが求められています」</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>県全体では令和4年度実績44市町村が設置済みであり、会津圏域の2か所は大きく遅れている。本村の未設置は圏域全体の課題。県は相談支援アドバイザーを活用した設置支援を方策に掲げており、4町村での広域設置の検討にこれを求める。計画素案 第4章（6）に反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>施設入所者の地域生活移行</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>令和4年度末の施設入所者278人、令和8年度末の地域生活移行者9人（3％以上）、削減見込12人（4％以上）、令和8年度末266人。課題は障がいの重度化・高齢化と重度障がい者・高齢障がい者の受け皿</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>本村の施設入所者は4人。圏域目標と同じ3％・4％を当てるといずれも1人未満になる。村の移行0人・削減0人は圏域目標と矛盾しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>一般就労への移行</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>令和3年度16人→令和8年度32人（2.0倍）。うち就労移行支援6→11人、A型3→7人、B型7→14人。就労定着支援の利用者数10→24人（2.4倍）。令和8年度の就労移行支援事業所2か所・就労定着支援事業所2か所はいずれも一般就労移行5割以上・定着率7割以上が100％</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>本村の一般就労移行者数は少数。圏域の目標倍率（2.0倍）は国の基本指針（1.28倍以上）を大きく上回る。第4章（3）の目標設定で圏域の水準に触れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>新たに必要となる事業所数</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>令和5年4月1日→令和8年度：就労選択支援0→2か所（新設）、就労継続支援A型6→8か所、同B型30→32か所、共同生活援助34→36か所、自立生活援助0→1か所（新設）、自立訓練（機能訓練）0→1か所（新設）、就労移行支援2→3か所、就労定着支援2→3か所、生活介護22→23か所。施設入所支援4か所・療養介護0か所・短期入所（福祉系11・医療系1）は据え置き</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>本村が圏域の事業所を利用して確保する前提は、この整備計画に沿う。計画素案 第5章8に反映。第8期県計画の公表後に同じ箇所を見直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>障がい児支援の整備状況</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>令和5年4月1日現在。児童発達支援センター1か所（会津若松市）、児童発達支援事業所20か所（会津若松市13・喜多方市3・猪苗代町1・会津坂下町2・湯川村1）、放課後等デイサービス23か所（会津若松市14・喜多方市3・磐梯町1・猪苗代町1・会津坂下町2・湯川村1・会津美里町1）、保育所等訪問支援6か所（会津若松市）、障害児相談支援18か所、短期入所（福祉型・児童利用可）1か所（猪苗代町）、福祉型障害児入所施設1か所（猪苗代町）。医療型の児童発達支援センター・事業所・入所施設はいずれも0か所</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>児童発達支援センターと保育所等訪問支援は会津若松市のみで本村から遠い。短期入所（児童）と福祉型障害児入所施設は猪苗代町＝会津北部圏域の内。第4章（4）の4つの中核機能へのアクセス確保の具体に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>障がい児支援の見込量</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>令和8年度（圏域）：障害児相談支援653人、児童発達支援257人（1,320人日／月）、放課後等デイサービス458人（4,424人日／月）、保育所等訪問支援120人（108人日／月）、居宅訪問型児童発達支援2人。必要な事業所数は児童発達支援24か所・放課後等デイサービス27か所・保育所等訪問支援6か所</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>本村の障がい児の見込量（児童発達支援1人・放課後等デイサービス2人等）は圏域の規模に対してごく小さい。確保は圏域の事業所に依存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>圏域の推進体制</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>会津障がい保健福祉圏域連絡会の下部組織に8つのワーキンググループ（精神保健福祉、就労、事業所、重点検討事項ほか）を置き、ワーキンググループ長会議とサービス調整会議で横の連携を図る。相談支援事業所は圏域に22か所</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>本村が圏域で課題を持ち込む先が具体的に分かる。強度行動障害の支援、権利擁護、BCP・個別避難計画もワーキンググループでの検討事項とされている</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1487,7 +1729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1606,12 +1848,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>福島県障がい者計画（第5次）の計画期間（満了年度）と、次期計画の策定予定</t>
+          <t>第5次福島県障がい者計画の次期計画（第6次）の策定予定</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>本計画期間（令和9〜11年度）が県障がい者計画の期間内に収まるかどうかで、第1章2の整合の書き方が変わる。令和4年度から9年間（令和12年度まで）と確認しているが原典を見ていない</t>
+          <t>計画期間は令和4〜12年度の9年間であることを原典で確認したため、本計画期間（令和9〜11年度）は県障がい者計画の期間内に完全に収まる（当初の照会事項は解決）。残るのは、県が令和12年度の満了に向けていつから次期計画の検討に入るかで、本村の第5次障がい者計画（令和12年度以降）の立ち上げ時期に関わる</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1621,7 +1863,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
     </row>
@@ -1688,13 +1930,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1808,152 +2050,196 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>第4章（6）</t>
+          <t>第1章2</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>基幹相談支援センターについて、県全体59市町村（令和4年度実績44市町村）・会津圏域13市町村の目標と、圏域の設置が2か所（会津若松市・喜多方市）にとどまる事実、県の相談支援アドバイザーによる設置支援を追記</t>
+          <t>「■　県障がい者計画の基本目標と本計画の施策体系」を新設。村の7つの基本施策と県の9つの重点施策の対応表を置き、県の重点施策⑦（アクセシビリティの向上）に正面から対応する基本施策がないこと、特に⑶行政等における配慮の定着に記述がないことを明記。県条例2本を根拠として掲げた</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>第7期県計画 第3の5（p.34）・会津圏域計画6(4)・第3期県計画の会津圏域計画（障がい児支援）3</t>
+          <t>第5次福島県障がい者計画 第1章第2・第3・第4・第5、第3章第1</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>設置市町村数と圏域の設置実績を原典と機械で照合</t>
+          <t>県の9つの重点施策が対応表に残らず現れることと、引用11件が原典に実在することを機械で照合</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>第4章（4）</t>
+          <t>第3章4</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>会津圏域の障がい児支援事業所の所在を表で追記。児童発達支援センターと保育所等訪問支援は会津若松市のみ、短期入所（児童）と福祉型障害児入所施設は猪苗代町</t>
+          <t>県の重点施策⑦のうち「行政等における配慮の定着」が第8期で加わる視点の対応表に現れないことを注記し、第1章2の検討事項に送った</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第3期福島県障がい児福祉計画 会津圏域計画（障がい児支援）3</t>
+          <t>第5次福島県障がい者計画 第3章第1</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>事業所数と市町村ごとの内訳を原典と機械で照合</t>
+          <t>第1章2の記述と食い違わないことを本ブック01dシートで対照</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>第5章8</t>
+          <t>第4章（6）</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>会津圏域が令和8年度までに新たに必要とする事業所数を追記（就労選択支援2か所の新設、就労継続支援A型6→8・B型30→32、共同生活援助34→36ほか）</t>
+          <t>基幹相談支援センターについて、県全体59市町村（令和4年度実績44市町村）・会津圏域13市町村の目標と、圏域の設置が2か所（会津若松市・喜多方市）にとどまる事実、県の相談支援アドバイザーによる設置支援を追記</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>第7期県計画 会津圏域計画8</t>
+          <t>第7期県計画 第3の5（p.34）・会津圏域計画6(4)・第3期県計画の会津圏域計画（障がい児支援）3</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>事業所数の推移を原典と機械で照合</t>
+          <t>設置市町村数と圏域の設置実績を原典と機械で照合</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>第5章1</t>
+          <t>第4章（4）</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>告示 第三の二の2㈠が「設定するものとする」とした2要件（継続入所者の控除・保育所等における障害児の受入れ体制）を算定方法の根拠の表に追加し、村への照会を最優先として明記</t>
+          <t>会津圏域の障がい児支援事業所の所在を表で追記。児童発達支援センターと保育所等訪問支援は会津若松市のみ、短期入所（児童）と福祉型障害児入所施設は猪苗代町</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>告示 第三の二の2㈠。見込量算定MECEチェックの指摘E-1・E-2</t>
+          <t>第3期福島県障がい児福祉計画 会津圏域計画（障がい児支援）3</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>素案の本文に2要件が現れることを確認（告示本文のPDFと照合）</t>
+          <t>事業所数と市町村ごとの内訳を原典と機械で照合</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>第5章7・第5章冒頭</t>
+          <t>第5章8</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>廃止区分「医療型児童発達支援」を≪サービスの内容≫とサービス区分表から削除し、②〜⑦の番号を繰り上げ</t>
+          <t>会津圏域が令和8年度までに新たに必要とする事業所数を追記（就労選択支援2か所の新設、就労継続支援A型6→8・B型30→32、共同生活援助34→36ほか）</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>令和4年法律第66号による児童福祉法の改正（令和6年4月1日施行）。見込量MECEチェックの指摘X-1</t>
+          <t>第7期県計画 会津圏域計画8</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>生成器の自己点検で、表の行名に廃止区分がないこと及びサービスの内容が①〜⑥の連番であることを確認</t>
+          <t>事業所数の推移を原典と機械で照合</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>第5章冒頭・第5章7・第5章9</t>
+          <t>第5章1</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>「R6～R8実績」「R9～R11見込量」等の略記の年度表記を令和表記に統一</t>
+          <t>告示 第三の二の2㈠が「設定するものとする」とした2要件（継続入所者の控除・保育所等における障害児の受入れ体制）を算定方法の根拠の表に追加し、村への照会を最優先として明記</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>注記が差し替え前の列名を指したままになっていた</t>
+          <t>告示 第三の二の2㈠。見込量算定MECEチェックの指摘E-1・E-2</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>生成器の自己点検で、表頭と注記に略記の年度表記がないことを確認</t>
+          <t>素案の本文に2要件が現れることを確認（告示本文のPDFと照合）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>第5章7・第5章冒頭</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>廃止区分「医療型児童発達支援」を≪サービスの内容≫とサービス区分表から削除し、②〜⑦の番号を繰り上げ</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>令和4年法律第66号による児童福祉法の改正（令和6年4月1日施行）。見込量MECEチェックの指摘X-1</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>生成器の自己点検で、表の行名に廃止区分がないこと及びサービスの内容が①〜⑥の連番であることを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>第5章冒頭・第5章7・第5章9</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>「R6～R8実績」「R9～R11見込量」等の略記の年度表記を令和表記に統一</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>注記が差し替え前の列名を指したままになっていた</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>生成器の自己点検で、表頭と注記に略記の年度表記がないことを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t>生成器</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>計画素案の生成器に保存前の自己点検（verify_output）を追加。見込量表5件がデータ行を持つこと、廃止区分が行名に残らないこと、番号が連番であることを保存前に確かめる</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>注記ボックスは1x1の表であるため、見込量表の直前に差し込むと見込量表と取り違えられ、見込量が消えたまま警告なく保存される。本日の作業で実際に起こした</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>点検に落ちることを確認した上で原因を直した</t>
         </is>

--- a/output/北塩原村_福島県計画との整合.xlsx
+++ b/output/北塩原村_福島県計画との整合.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>本村に独自の条例がないため、差別の解消（基本施策①）と意思疎通支援はこれらの県条例を根拠として記述できる。第1章2の注記に明記</t>
+          <t>差別の解消（基本施策①）と意思疎通支援は、これらの県条例に加え、本村が令和7年4月に制定した「北塩原村手話言語条例」を根拠として記述できる。当初「本村に独自の条例がない」としていたが、令和8年10月10日の村ホームページの確認により誤りと分かった</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_福島県計画との整合.xlsx
+++ b/output/北塩原村_福島県計画との整合.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>本村に長期入院者がいる場合の地域移行の見通しを立てる材料。村及び会津保健所での実数の確認が前提（M-12）</t>
+          <t>本村に長期入院者がいる場合の地域移行の見通しを立てる材料。村及び会津保健所での実数の確認が前提（Ｍ-12）</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Ｍ-12</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
